--- a/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E97DE29F-DAE1-4831-A914-C46A96C6EDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{678F381E-8AC0-4B18-92ED-0F9BD91F6083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1494,7 +1494,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293AC66C-F904-49B8-9285-56BC335DFDF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84CC20B-0D29-44E2-A13B-07099603C930}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1551,7 +1551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DEE0472-8863-443E-83D7-3E53C5F46F59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67948041-BFF4-454D-A8FF-CD779F4350F7}">
   <dimension ref="B9:O49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2783,7 +2783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A67320D-C05C-4204-AAF9-B53F2369B34B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{168DD484-DF47-4D68-B85B-6A345589230C}">
   <dimension ref="B9:T101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5555,7 +5555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51BCE5A-D4ED-42ED-9534-3B81CB4E6E90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA2B1C9-458B-4603-983C-570474E1194E}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5599,7 +5599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE918F1-9E40-4F09-909B-2206E3CA3835}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFCADE9-6678-454F-8074-D9DFB9540023}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5648,7 +5648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9DA2E5-1583-43E4-A836-0514B73140B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4559E9F8-56C1-4A74-817E-E7A4009299C6}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5686,7 +5686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA302E5A-21BC-437C-AB63-CDACC387AC38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A152230-9CF8-46AF-8E3C-9EFAEE2670E2}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5774,7 +5774,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.62026666666666663</v>
+        <v>0.62026666666666674</v>
       </c>
       <c r="E15" t="s">
         <v>249</v>
@@ -5816,7 +5816,7 @@
         <v>37</v>
       </c>
       <c r="D18">
-        <v>0.57696666666666663</v>
+        <v>0.57696666666666674</v>
       </c>
       <c r="E18" t="s">
         <v>249</v>
@@ -5844,7 +5844,7 @@
         <v>37</v>
       </c>
       <c r="D20">
-        <v>0.53077499999999989</v>
+        <v>0.53077500000000011</v>
       </c>
       <c r="E20" t="s">
         <v>249</v>
@@ -5872,7 +5872,7 @@
         <v>37</v>
       </c>
       <c r="D22">
-        <v>0.6374333333333333</v>
+        <v>0.63743333333333341</v>
       </c>
       <c r="E22" t="s">
         <v>249</v>
@@ -5886,7 +5886,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.65194999999999992</v>
+        <v>0.65195000000000014</v>
       </c>
       <c r="E23" t="s">
         <v>249</v>
@@ -5900,7 +5900,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.61035000000000006</v>
+        <v>0.61034999999999995</v>
       </c>
       <c r="E24" t="s">
         <v>249</v>
@@ -5928,7 +5928,7 @@
         <v>37</v>
       </c>
       <c r="D26">
-        <v>0.62834999999999996</v>
+        <v>0.62835000000000008</v>
       </c>
       <c r="E26" t="s">
         <v>249</v>
@@ -5942,7 +5942,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.61771666666666669</v>
+        <v>0.61771666666666658</v>
       </c>
       <c r="E27" t="s">
         <v>249</v>
@@ -5970,7 +5970,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>0.52758333333333329</v>
+        <v>0.5275833333333334</v>
       </c>
       <c r="E29" t="s">
         <v>249</v>
@@ -6026,7 +6026,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.54595833333333332</v>
+        <v>0.54595833333333321</v>
       </c>
       <c r="E33" t="s">
         <v>249</v>
@@ -6054,7 +6054,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.629525</v>
+        <v>0.62952499999999989</v>
       </c>
       <c r="E35" t="s">
         <v>249</v>
@@ -6082,7 +6082,7 @@
         <v>37</v>
       </c>
       <c r="D37">
-        <v>0.53181666666666672</v>
+        <v>0.5318166666666666</v>
       </c>
       <c r="E37" t="s">
         <v>249</v>
@@ -6096,7 +6096,7 @@
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0.52934999999999999</v>
+        <v>0.5293500000000001</v>
       </c>
       <c r="E38" t="s">
         <v>249</v>
